--- a/attendance_system/students.xlsx
+++ b/attendance_system/students.xlsx
@@ -468,12 +468,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>B.Sc. CS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>III Year A</t>
+          <t>B.Sc. CS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -491,12 +491,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>B.Sc. CSDA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>III Year A</t>
+          <t>B.Sc. CSDA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -514,12 +514,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>B.com.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>III Year B</t>
+          <t>B.com.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -537,12 +537,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>B.com. CA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>II Year A</t>
+          <t>B.com. CA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -560,12 +560,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>B.com. PA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>II Year A</t>
+          <t>B.com. PA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -583,12 +583,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>B.com IT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>II Year B</t>
+          <t>B.com IT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -606,12 +606,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MECH</t>
+          <t>BBA CA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IV Year A</t>
+          <t>BBA CA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -629,12 +629,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MECH</t>
+          <t>B.Sc. CSHM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IV Year A</t>
+          <t>B.Sc. CSHM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -652,12 +652,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>B.Sc. IT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>I Year A</t>
+          <t>B.Sc. IT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -675,12 +675,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>B.Sc. CS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>I Year A</t>
+          <t>B.Sc. CS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -698,12 +698,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>B.com. CA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>III Year B</t>
+          <t>B.com. CA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>B.Sc. CSDA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>II Year B</t>
+          <t>B.Sc. CSDA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -744,12 +744,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>B.Sc. CS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>III Bsc</t>
+          <t>B.Sc. CS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -765,10 +765,14 @@
           <t>a. RB’ A</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B.Sc. CSDA</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Betch: 2023-2026</t>
+          <t>B.Sc. CSDA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -788,10 +792,14 @@
           <t>Www saikara ac in</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B.Sc. CSDA</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BSC CS&amp;DA</t>
+          <t>B.Sc. CSDA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -811,10 +819,14 @@
           <t>I SRUTHIKA.A</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B.Sc. CSDA</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Betch: 2023-2026</t>
+          <t>B.Sc. CSDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
